--- a/data/trans_orig/P6714-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6714-Clase-trans_orig.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W46"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se sienten comprometidos con su profesión en 2012</t>
+          <t>Población según si se sienten comprometidos con su profesión en 2012 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>4532</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -766,62 +766,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2107</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>4589</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>897</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4473</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>910</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8204</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>5733</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>990</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9306</t>
+          <t>9952</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13965</t>
+          <t>14176</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32974</t>
+          <t>31666</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5070</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19292</t>
+          <t>19830</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23610</t>
+          <t>23916</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45953</t>
+          <t>47072</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40690</t>
+          <t>41399</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70129</t>
+          <t>67698</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23976</t>
+          <t>23728</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46732</t>
+          <t>45837</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71508</t>
+          <t>71078</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108726</t>
+          <t>107578</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>203651</t>
+          <t>202993</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>236664</t>
+          <t>234877</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>135104</t>
+          <t>136330</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>160406</t>
+          <t>160209</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>347881</t>
+          <t>349519</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>388430</t>
+          <t>389428</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,64%</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>881</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8968</t>
+          <t>8687</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1795</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14001</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10661</t>
+          <t>10297</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16686</t>
+          <t>17979</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17598</t>
+          <t>19113</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39005</t>
+          <t>39278</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20257</t>
+          <t>20815</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41630</t>
+          <t>41028</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>44805</t>
+          <t>44452</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>74572</t>
+          <t>72502</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,12%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43376</t>
+          <t>44290</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72467</t>
+          <t>72877</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35307</t>
+          <t>35909</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60125</t>
+          <t>59038</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87227</t>
+          <t>85470</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124177</t>
+          <t>123730</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>151731</t>
+          <t>149497</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>182311</t>
+          <t>183049</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>69387</t>
+          <t>70054</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>96227</t>
+          <t>97343</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,98%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>227641</t>
+          <t>227721</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>270698</t>
+          <t>270901</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,97%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>8998</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>4358</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>10383</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1969</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15036</t>
+          <t>14850</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11438</t>
+          <t>11599</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19948</t>
+          <t>19707</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19029</t>
+          <t>19329</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39288</t>
+          <t>40031</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10642</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25950</t>
+          <t>25848</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33891</t>
+          <t>32785</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>58972</t>
+          <t>58433</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52956</t>
+          <t>52628</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80952</t>
+          <t>81006</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13092</t>
+          <t>13258</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29413</t>
+          <t>29523</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>71443</t>
+          <t>69877</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>103151</t>
+          <t>101493</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,87%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>161266</t>
+          <t>160885</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>193172</t>
+          <t>194341</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57578</t>
+          <t>56657</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>78375</t>
+          <t>78502</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,52%</t>
+          <t>50,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>229324</t>
+          <t>228500</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>267097</t>
+          <t>264797</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,49%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>736</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8014</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3073</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14582</t>
+          <t>14318</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5240</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17454</t>
+          <t>17696</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8461</t>
+          <t>8063</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26447</t>
+          <t>25377</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18410</t>
+          <t>18019</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15217</t>
+          <t>15718</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>37204</t>
+          <t>38033</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>74284</t>
+          <t>75196</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>111816</t>
+          <t>110922</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37785</t>
+          <t>39122</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>64641</t>
+          <t>64249</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>125283</t>
+          <t>122783</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>169784</t>
+          <t>168894</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>83916</t>
+          <t>85912</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>121192</t>
+          <t>121132</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>81630</t>
+          <t>82955</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>116159</t>
+          <t>116552</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>176872</t>
+          <t>176565</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>226070</t>
+          <t>224416</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>30,96%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>191967</t>
+          <t>191565</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>235099</t>
+          <t>235194</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,07%</t>
+          <t>55,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>113890</t>
+          <t>112549</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>148983</t>
+          <t>146305</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>315300</t>
+          <t>315789</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>369703</t>
+          <t>371765</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,29%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7896</t>
+          <t>8130</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23414</t>
+          <t>24193</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3179</t>
+          <t>2369</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14581</t>
+          <t>12816</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13398</t>
+          <t>12576</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>31527</t>
+          <t>30858</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>13510</t>
+          <t>12617</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31744</t>
+          <t>30845</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14164</t>
+          <t>14578</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33042</t>
+          <t>33176</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>32163</t>
+          <t>31929</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>57673</t>
+          <t>57091</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16517</t>
+          <t>15857</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>35039</t>
+          <t>33693</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>33411</t>
+          <t>33254</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>57847</t>
+          <t>57013</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>51605</t>
+          <t>54203</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>82456</t>
+          <t>83653</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>33447</t>
+          <t>33439</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>55210</t>
+          <t>56719</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,34%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>29104</t>
+          <t>28521</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>51927</t>
+          <t>52344</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>67735</t>
+          <t>68186</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>100437</t>
+          <t>100913</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,9%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>37837</t>
+          <t>37372</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>60191</t>
+          <t>60525</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>49529</t>
+          <t>49499</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>75539</t>
+          <t>77034</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>93387</t>
+          <t>94124</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>127974</t>
+          <t>129934</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,79%</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4131,107 +4131,107 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22549</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14481</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33441</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17738</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10896</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28388</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>40287</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28500</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55319</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -4244,107 +4244,107 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50441</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>37814</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66223</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>40125</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28133</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55537</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>78</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>90567</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72187</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>113893</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -4357,107 +4357,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>183</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>194189</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>168176</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>221423</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>143</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>154624</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>133635</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>177963</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>326</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>348813</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>314423</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>388836</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -4470,107 +4470,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>310</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>322453</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>291319</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>359715</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>225</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>239243</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>213748</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>267521</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>535</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>561696</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>520028</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>605764</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -4583,107 +4583,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>773</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>828096</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>788887</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>865000</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,41%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>453</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>493001</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>460768</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>524402</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,18%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1321096</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1268668</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1371607</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,06%</t>
         </is>
       </c>
     </row>
@@ -4696,804 +4696,121 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1417729</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1417729</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1417729</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>872</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>944731</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>944731</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>944731</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2362459</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2362459</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2362459</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Nunca</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>22549</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>13967</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>33577</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>1,59%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>17738</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>10403</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>27404</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>40287</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>29857</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>56367</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Solo alguna vez</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>50441</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>37093</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>67962</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>4,79%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>40125</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>28260</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>54799</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>90567</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>70117</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>111170</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>4,71%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Algunas veces</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>194189</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>170009</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>223968</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>13,7%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>11,99%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>15,8%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>154624</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>133460</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>181280</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>16,37%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>14,13%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>19,19%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>326</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>348813</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>315519</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>387436</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>14,76%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>13,36%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>16,4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Muchas veces</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>322453</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>289762</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>356002</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>22,74%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>20,44%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>25,11%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>239243</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>211470</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>268045</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>25,32%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>22,38%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>28,37%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>561696</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>523105</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>608341</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>23,78%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>22,14%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>25,75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n"/>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Siempre</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>773</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>828096</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>786794</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>865281</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>58,41%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>55,5%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>61,03%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>453</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>493001</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>457325</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>523812</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>52,18%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>48,41%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>55,45%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>1226</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>1321096</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>1265877</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>1372103</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>55,92%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>53,58%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>58,08%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>1332</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>1417729</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>1417729</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1417729</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>872</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>944731</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>944731</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>944731</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>2204</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>2362459</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>2362459</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>2362459</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A40:A45"/>
     <mergeCell ref="A4:A9"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A34:A39"/>
@@ -5513,7 +4830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W46"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5544,7 +4861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se sienten comprometidos con su profesión en 2016</t>
+          <t>Población según si se sienten comprometidos con su profesión en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5744,7 +5061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5759,7 +5076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5779,7 +5096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>4594</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5794,7 +5111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5814,7 +5131,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8438</t>
+          <t>7136</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5829,7 +5146,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6607</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21893</t>
+          <t>21413</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5867,12 +5184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5887,12 +5204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10731</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5907,7 +5224,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5922,12 +5239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9315</t>
+          <t>9568</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26129</t>
+          <t>26271</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5937,12 +5254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5282,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14722</t>
+          <t>15057</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35419</t>
+          <t>35223</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5980,12 +5297,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6000,12 +5317,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10566</t>
+          <t>10661</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>27782</t>
+          <t>26557</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6015,12 +5332,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6035,12 +5352,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30498</t>
+          <t>29820</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56459</t>
+          <t>56599</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6050,12 +5367,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +5395,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37433</t>
+          <t>38415</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63552</t>
+          <t>64356</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6093,12 +5410,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6113,12 +5430,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24036</t>
+          <t>23532</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46114</t>
+          <t>45403</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6128,12 +5445,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6148,12 +5465,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>67458</t>
+          <t>66865</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101604</t>
+          <t>100851</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6163,12 +5480,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +5508,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>175049</t>
+          <t>173816</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>206292</t>
+          <t>204335</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6206,12 +5523,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>73,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6226,12 +5543,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>144105</t>
+          <t>144358</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>171120</t>
+          <t>171336</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6241,12 +5558,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6261,12 +5578,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>328063</t>
+          <t>329435</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>368417</t>
+          <t>371156</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6276,12 +5593,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>75,36%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +5738,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1732</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9911</t>
+          <t>9877</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6436,12 +5753,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6456,12 +5773,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2239</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13278</t>
+          <t>13459</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6476,7 +5793,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6491,12 +5808,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>5825</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>19780</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6506,12 +5823,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +5851,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17741</t>
+          <t>18034</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6549,12 +5866,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6569,12 +5886,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13563</t>
+          <t>13740</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30673</t>
+          <t>30740</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6584,12 +5901,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6604,12 +5921,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22136</t>
+          <t>21664</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43778</t>
+          <t>43938</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6619,12 +5936,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +5964,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33194</t>
+          <t>33833</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59119</t>
+          <t>59246</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6662,12 +5979,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6682,12 +5999,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22299</t>
+          <t>22413</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43908</t>
+          <t>42980</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6697,12 +6014,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6717,12 +6034,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>61503</t>
+          <t>60663</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>94244</t>
+          <t>94831</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6732,12 +6049,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6077,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55347</t>
+          <t>55400</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84942</t>
+          <t>84312</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6775,12 +6092,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6795,12 +6112,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44212</t>
+          <t>43525</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70192</t>
+          <t>69686</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6810,12 +6127,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,1%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6830,12 +6147,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>106054</t>
+          <t>107480</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>146186</t>
+          <t>143607</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6845,12 +6162,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,15%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6190,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98058</t>
+          <t>100710</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131478</t>
+          <t>132183</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6888,12 +6205,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6908,12 +6225,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59016</t>
+          <t>60668</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>88070</t>
+          <t>88881</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6923,12 +6240,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6943,12 +6260,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>165014</t>
+          <t>167868</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>211601</t>
+          <t>209286</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6958,12 +6275,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,31%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +6420,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>2212</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13785</t>
+          <t>15973</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7118,12 +6435,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7138,12 +6455,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7153,12 +6470,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7173,12 +6490,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14763</t>
+          <t>15307</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7188,12 +6505,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +6533,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7285</t>
+          <t>7097</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23955</t>
+          <t>22923</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7231,12 +6548,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7256,7 +6573,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7271,7 +6588,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7286,12 +6603,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24031</t>
+          <t>24159</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7301,12 +6618,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +6646,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22967</t>
+          <t>22601</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44485</t>
+          <t>43983</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7344,12 +6661,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7364,12 +6681,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>876</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>7816</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7379,12 +6696,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7399,12 +6716,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>25260</t>
+          <t>24059</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>46895</t>
+          <t>48369</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7414,12 +6731,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,0%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +6759,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52181</t>
+          <t>51811</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80259</t>
+          <t>79479</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7457,12 +6774,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7477,12 +6794,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18504</t>
+          <t>18639</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34008</t>
+          <t>34250</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7492,12 +6809,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,61%</t>
+          <t>50,97%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7512,12 +6829,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>76995</t>
+          <t>76014</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>107607</t>
+          <t>107792</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7527,12 +6844,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,89%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +6872,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>85369</t>
+          <t>85367</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>114406</t>
+          <t>115620</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7575,7 +6892,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,66%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7590,12 +6907,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29376</t>
+          <t>29096</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>45365</t>
+          <t>44714</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7605,12 +6922,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7625,12 +6942,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>121063</t>
+          <t>120120</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>154675</t>
+          <t>154698</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7640,7 +6957,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -7785,12 +7102,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11161</t>
+          <t>11111</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29282</t>
+          <t>29066</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7800,12 +7117,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7820,12 +7137,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14348</t>
+          <t>14404</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7835,12 +7152,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7855,12 +7172,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17030</t>
+          <t>16225</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37957</t>
+          <t>37330</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7870,12 +7187,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7215,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11887</t>
+          <t>11475</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28781</t>
+          <t>28601</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7913,12 +7230,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7933,12 +7250,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19164</t>
+          <t>19314</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>38901</t>
+          <t>39204</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7948,12 +7265,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7968,12 +7285,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>33711</t>
+          <t>34848</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>60311</t>
+          <t>60052</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7983,12 +7300,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -8011,12 +7328,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>99982</t>
+          <t>98035</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>137724</t>
+          <t>137041</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8026,12 +7343,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8046,12 +7363,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>54158</t>
+          <t>53512</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>80719</t>
+          <t>82209</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8061,12 +7378,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8081,12 +7398,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>158971</t>
+          <t>160363</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>209178</t>
+          <t>208773</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8096,12 +7413,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -8124,12 +7441,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>134537</t>
+          <t>135951</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>177337</t>
+          <t>176334</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8139,12 +7456,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8159,12 +7476,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>111762</t>
+          <t>111269</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>148451</t>
+          <t>147252</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8174,12 +7491,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8194,12 +7511,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>257760</t>
+          <t>259523</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>314680</t>
+          <t>313982</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8209,12 +7526,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,65%</t>
         </is>
       </c>
     </row>
@@ -8237,12 +7554,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>157084</t>
+          <t>157141</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>199673</t>
+          <t>202031</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8252,12 +7569,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8272,12 +7589,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>119141</t>
+          <t>121165</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>155549</t>
+          <t>158488</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8287,12 +7604,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8307,12 +7624,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>288740</t>
+          <t>288404</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>344895</t>
+          <t>347134</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8322,12 +7639,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,52%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +7784,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14423</t>
+          <t>14645</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8482,12 +7799,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8502,12 +7819,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>7756</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>22001</t>
+          <t>21683</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8517,12 +7834,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8537,12 +7854,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13717</t>
+          <t>13541</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30770</t>
+          <t>31034</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8552,12 +7869,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -8580,12 +7897,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11673</t>
+          <t>12103</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>31059</t>
+          <t>30602</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8595,12 +7912,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8615,12 +7932,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13537</t>
+          <t>13562</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>29700</t>
+          <t>30729</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8630,12 +7947,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8650,12 +7967,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>28648</t>
+          <t>28951</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>53154</t>
+          <t>54525</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8665,12 +7982,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,92%</t>
         </is>
       </c>
     </row>
@@ -8693,12 +8010,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>53818</t>
+          <t>53464</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>81781</t>
+          <t>82506</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8708,12 +8025,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8728,12 +8045,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>53164</t>
+          <t>51293</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>80325</t>
+          <t>78595</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8743,12 +8060,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8763,12 +8080,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>114193</t>
+          <t>116148</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>151842</t>
+          <t>152464</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8778,12 +8095,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,94%</t>
         </is>
       </c>
     </row>
@@ -8806,12 +8123,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>28765</t>
+          <t>29028</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>51080</t>
+          <t>51716</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8821,12 +8138,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8841,12 +8158,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>35841</t>
+          <t>35765</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>60084</t>
+          <t>59853</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8856,12 +8173,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8876,12 +8193,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>71665</t>
+          <t>70096</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>103804</t>
+          <t>104932</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8891,12 +8208,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -8919,12 +8236,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>46546</t>
+          <t>47803</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>73691</t>
+          <t>75038</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8934,12 +8251,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>37,99%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8954,12 +8271,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>38522</t>
+          <t>39597</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>64164</t>
+          <t>62793</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8969,12 +8286,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8989,12 +8306,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>93122</t>
+          <t>93667</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>127805</t>
+          <t>129044</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9004,12 +8321,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
@@ -9129,7 +8446,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9139,107 +8456,107 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>38639</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>26995</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>53451</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27505</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17905</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39650</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>66143</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>50407</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>84742</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -9252,107 +8569,107 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>74934</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>58090</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>95612</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>74</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>74096</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>59967</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>92322</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>142</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>149030</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>125880</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>174172</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -9365,107 +8682,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>260</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>286215</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>254758</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>317637</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>187</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>184719</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>162145</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>208778</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>447</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>470934</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>429912</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>513227</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -9478,107 +8795,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>359</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>377909</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>345810</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>410788</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>289</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>293214</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>265397</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>322935</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>648</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>671123</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>624476</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>718286</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -9591,107 +8908,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>601</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>644625</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>605890</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>683259</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>437</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>456685</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>425754</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>488089</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,1%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1038</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1101310</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1054175</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1158521</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>47,12%</t>
         </is>
       </c>
     </row>
@@ -9704,804 +9021,121 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Nunca</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>38639</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>27043</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>52696</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>27505</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>18192</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>38542</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>66143</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>50731</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>83687</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>2,06%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Solo alguna vez</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>74934</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>59030</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>97659</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>6,87%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>74096</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>59557</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>92945</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>7,15%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>5,75%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>8,97%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>149030</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>126367</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>173948</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Algunas veces</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>260</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>286215</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>255462</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>318984</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>20,12%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>17,96%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>22,43%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>184719</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>161914</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>208845</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>17,83%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>15,63%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>20,15%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>447</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>470934</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>435129</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>509577</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>19,16%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>17,7%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>20,73%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Muchas veces</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>359</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>377909</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>346522</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>417308</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>26,57%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>24,36%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>29,34%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>293214</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>265507</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>322412</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>28,3%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>25,62%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>31,11%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>671123</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>621836</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>715641</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>27,3%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>25,29%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>29,11%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n"/>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Siempre</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>601</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>644625</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>602258</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>680039</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>45,32%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>42,34%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>47,81%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>437</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>456685</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>428668</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>492500</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>44,07%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>41,37%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>47,53%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>1038</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>1101310</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>1056045</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>1153877</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>44,8%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>42,95%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>46,93%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>2335</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A40:A45"/>
     <mergeCell ref="A4:A9"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A34:A39"/>

--- a/data/trans_orig/P6714-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6714-Clase-trans_orig.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4476</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4589</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>941</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5733</t>
+          <t>5198</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>992</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>10261</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14176</t>
+          <t>14862</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31666</t>
+          <t>33299</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19830</t>
+          <t>20298</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23916</t>
+          <t>23557</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47072</t>
+          <t>45393</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41399</t>
+          <t>41631</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67698</t>
+          <t>69477</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23728</t>
+          <t>23830</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45837</t>
+          <t>46888</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71078</t>
+          <t>70748</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107578</t>
+          <t>105582</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,32%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>202993</t>
+          <t>202356</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>234877</t>
+          <t>234233</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>136330</t>
+          <t>134326</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>160209</t>
+          <t>159351</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>69,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>349519</t>
+          <t>348977</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>389428</t>
+          <t>388425</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>5446</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,7 +1453,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7655</t>
+          <t>7542</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>965</t>
+          <t>964</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>9431</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>992</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10297</t>
+          <t>10377</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2868</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17979</t>
+          <t>17859</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19113</t>
+          <t>18216</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>39278</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20815</t>
+          <t>21428</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41028</t>
+          <t>42921</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>44452</t>
+          <t>43468</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>72502</t>
+          <t>73971</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44290</t>
+          <t>43954</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>72877</t>
+          <t>71809</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>27,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35909</t>
+          <t>35014</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59038</t>
+          <t>59179</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85470</t>
+          <t>86207</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123730</t>
+          <t>123438</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>149497</t>
+          <t>150677</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>183049</t>
+          <t>182868</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>71,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70054</t>
+          <t>69556</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>97343</t>
+          <t>96430</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>227721</t>
+          <t>228157</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>270901</t>
+          <t>271393</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>64,08%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8998</t>
+          <t>9108</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>6364</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10383</t>
+          <t>10787</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14850</t>
+          <t>14581</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1068</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11599</t>
+          <t>11906</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19707</t>
+          <t>20820</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19329</t>
+          <t>19598</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>40031</t>
+          <t>38554</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>11267</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25848</t>
+          <t>26202</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>32785</t>
+          <t>33462</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>58433</t>
+          <t>59357</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,13%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52628</t>
+          <t>50822</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81006</t>
+          <t>79056</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13258</t>
+          <t>13347</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29523</t>
+          <t>29198</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>69877</t>
+          <t>71678</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101493</t>
+          <t>102945</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,24%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>160885</t>
+          <t>162815</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>194341</t>
+          <t>195411</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56657</t>
+          <t>57019</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>78502</t>
+          <t>77834</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>70,24%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>228500</t>
+          <t>226713</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>264797</t>
+          <t>265281</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>67,61%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>731</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>7405</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3100</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14318</t>
+          <t>14020</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5022</t>
+          <t>4963</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17696</t>
+          <t>17579</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8063</t>
+          <t>8080</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25377</t>
+          <t>25493</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>4477</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>18019</t>
+          <t>19785</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15718</t>
+          <t>15656</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>38033</t>
+          <t>36955</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>75196</t>
+          <t>76649</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>110922</t>
+          <t>112499</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>39122</t>
+          <t>39208</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>64249</t>
+          <t>65315</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>122783</t>
+          <t>122228</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>168894</t>
+          <t>170175</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,48%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>85912</t>
+          <t>85117</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>121132</t>
+          <t>122010</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>82955</t>
+          <t>82954</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>116552</t>
+          <t>117127</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>176565</t>
+          <t>179309</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>224416</t>
+          <t>227541</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>191565</t>
+          <t>193640</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>235194</t>
+          <t>235384</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,87%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>112549</t>
+          <t>113941</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>146305</t>
+          <t>148890</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>315789</t>
+          <t>316904</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>371765</t>
+          <t>374404</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,65%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>7879</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24193</t>
+          <t>23580</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2369</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12816</t>
+          <t>13305</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>12576</t>
+          <t>12649</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>30858</t>
+          <t>31837</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,75%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12617</t>
+          <t>13940</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30845</t>
+          <t>31759</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14578</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33176</t>
+          <t>32983</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>31929</t>
+          <t>32352</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>57091</t>
+          <t>57822</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>15857</t>
+          <t>16278</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>33693</t>
+          <t>33839</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>33254</t>
+          <t>32333</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>57013</t>
+          <t>56136</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>54203</t>
+          <t>54014</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>83653</t>
+          <t>83992</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>33439</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>56719</t>
+          <t>56212</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>28521</t>
+          <t>28263</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>52344</t>
+          <t>51451</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>68186</t>
+          <t>67023</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>100913</t>
+          <t>98687</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,22%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>37372</t>
+          <t>36799</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>60525</t>
+          <t>61026</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>49499</t>
+          <t>50292</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>77034</t>
+          <t>76468</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>94124</t>
+          <t>95078</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>129934</t>
+          <t>129437</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,63%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14481</t>
+          <t>13742</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>33441</t>
+          <t>34170</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,82 +4156,82 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>17738</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>10488</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>27858</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>40287</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>30285</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>55743</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
           <t>2,36%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>17738</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>10896</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>28388</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>40287</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>28500</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>55319</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>37814</t>
+          <t>37009</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>66223</t>
+          <t>66184</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>28133</t>
+          <t>28576</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>55537</t>
+          <t>55752</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>72187</t>
+          <t>71279</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>113893</t>
+          <t>112385</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>168176</t>
+          <t>168757</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>221423</t>
+          <t>224994</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>133635</t>
+          <t>132604</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>177963</t>
+          <t>182021</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>314423</t>
+          <t>316369</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>388836</t>
+          <t>386894</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>291319</t>
+          <t>288603</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>359715</t>
+          <t>357218</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>213748</t>
+          <t>212703</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>267521</t>
+          <t>267655</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>520028</t>
+          <t>521384</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>605764</t>
+          <t>603596</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,55%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>788887</t>
+          <t>789635</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>865000</t>
+          <t>867498</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>460768</t>
+          <t>459151</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>524402</t>
+          <t>522657</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1268668</t>
+          <t>1272053</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1371607</t>
+          <t>1370481</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,01%</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>7789</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4594</t>
+          <t>5108</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7136</t>
+          <t>8313</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21413</t>
+          <t>21226</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>949</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9568</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>27056</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15057</t>
+          <t>15293</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35223</t>
+          <t>36438</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10661</t>
+          <t>10359</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26557</t>
+          <t>27756</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>29820</t>
+          <t>30173</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56599</t>
+          <t>58218</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38415</t>
+          <t>36950</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>64356</t>
+          <t>63617</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23532</t>
+          <t>24237</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45403</t>
+          <t>45417</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66865</t>
+          <t>68230</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100851</t>
+          <t>101238</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>173816</t>
+          <t>174096</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>204335</t>
+          <t>205623</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>144358</t>
+          <t>145345</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>171336</t>
+          <t>171055</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>329435</t>
+          <t>326899</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>371156</t>
+          <t>367828</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>74,68%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1779</t>
+          <t>1733</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9877</t>
+          <t>10695</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2228</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13459</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19780</t>
+          <t>19888</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18034</t>
+          <t>18662</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5866,47 +5866,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>7,65%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>21208</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>13972</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>30621</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>11,21%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>7,39%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>21208</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>13740</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>30740</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>11,21%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>7,26%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>21664</t>
+          <t>21306</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43938</t>
+          <t>43182</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>33833</t>
+          <t>32308</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>59246</t>
+          <t>58463</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22413</t>
+          <t>23206</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42980</t>
+          <t>43848</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>60663</t>
+          <t>61784</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>94831</t>
+          <t>92986</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,46%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55400</t>
+          <t>54493</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84312</t>
+          <t>83497</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>43525</t>
+          <t>43495</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69686</t>
+          <t>70684</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107480</t>
+          <t>105034</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143607</t>
+          <t>143868</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,21%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>100710</t>
+          <t>99506</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>132183</t>
+          <t>132262</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60668</t>
+          <t>60326</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>88881</t>
+          <t>88103</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>167868</t>
+          <t>169696</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>209286</t>
+          <t>211753</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,88%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2212</t>
+          <t>2140</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15973</t>
+          <t>13682</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>2147</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15307</t>
+          <t>13456</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7097</t>
+          <t>7697</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>22923</t>
+          <t>23503</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7811</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24159</t>
+          <t>24295</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22601</t>
+          <t>22995</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43983</t>
+          <t>43851</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>880</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7816</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24059</t>
+          <t>24288</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48369</t>
+          <t>48396</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,01%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51811</t>
+          <t>52052</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79479</t>
+          <t>79521</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18639</t>
+          <t>18530</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34250</t>
+          <t>34589</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>76014</t>
+          <t>76783</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>107792</t>
+          <t>109431</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>85367</t>
+          <t>85814</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>115620</t>
+          <t>116369</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29096</t>
+          <t>28955</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44714</t>
+          <t>45076</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>120120</t>
+          <t>119500</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>154698</t>
+          <t>153282</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>53,89%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11111</t>
+          <t>10718</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29066</t>
+          <t>28996</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2874</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>16226</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16225</t>
+          <t>16831</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37330</t>
+          <t>37528</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11475</t>
+          <t>11875</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28601</t>
+          <t>29235</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19314</t>
+          <t>19088</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>39204</t>
+          <t>38541</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>34848</t>
+          <t>35449</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>60052</t>
+          <t>60904</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>98035</t>
+          <t>99156</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>137041</t>
+          <t>137499</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>53512</t>
+          <t>54069</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>82209</t>
+          <t>83889</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>160363</t>
+          <t>161546</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>208773</t>
+          <t>210892</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>135951</t>
+          <t>135778</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>176334</t>
+          <t>178543</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>111269</t>
+          <t>112107</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>147252</t>
+          <t>149515</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>259523</t>
+          <t>256973</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>313982</t>
+          <t>314150</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,67%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>157141</t>
+          <t>155242</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>202031</t>
+          <t>197927</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>121165</t>
+          <t>119275</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>158488</t>
+          <t>154819</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>43,06%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>288404</t>
+          <t>286467</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>347134</t>
+          <t>345637</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,34%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3235</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14645</t>
+          <t>14349</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7756</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21683</t>
+          <t>20848</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>13541</t>
+          <t>13023</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>31034</t>
+          <t>31434</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -7897,12 +7897,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>12103</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>30602</t>
+          <t>30569</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7932,12 +7932,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>13562</t>
+          <t>12520</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>30729</t>
+          <t>30705</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7947,12 +7947,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7967,12 +7967,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>28951</t>
+          <t>27716</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>54525</t>
+          <t>52187</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7982,12 +7982,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,33%</t>
         </is>
       </c>
     </row>
@@ -8010,12 +8010,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>53464</t>
+          <t>54681</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>82506</t>
+          <t>83182</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8025,12 +8025,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8045,12 +8045,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>51293</t>
+          <t>53168</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>78595</t>
+          <t>78659</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>116148</t>
+          <t>114502</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>152464</t>
+          <t>152520</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,95%</t>
         </is>
       </c>
     </row>
@@ -8123,12 +8123,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>29028</t>
+          <t>28549</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>51716</t>
+          <t>51420</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8138,12 +8138,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8158,12 +8158,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>35765</t>
+          <t>36203</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>59853</t>
+          <t>59255</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>70096</t>
+          <t>70387</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>104932</t>
+          <t>103382</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -8236,12 +8236,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>47803</t>
+          <t>47505</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>75038</t>
+          <t>73761</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8251,12 +8251,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8271,12 +8271,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>39597</t>
+          <t>39565</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>62793</t>
+          <t>63837</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>93667</t>
+          <t>91341</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>129044</t>
+          <t>128688</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,86%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>26995</t>
+          <t>27060</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>53451</t>
+          <t>53344</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>17905</t>
+          <t>17786</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>39650</t>
+          <t>39870</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>50407</t>
+          <t>51884</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>84742</t>
+          <t>86208</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -8579,12 +8579,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>58090</t>
+          <t>58390</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>95612</t>
+          <t>93531</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8614,12 +8614,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>59967</t>
+          <t>57886</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>92322</t>
+          <t>90988</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8649,12 +8649,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>125880</t>
+          <t>127850</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>174172</t>
+          <t>175386</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -8692,12 +8692,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>254758</t>
+          <t>257661</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>317637</t>
+          <t>319836</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8707,12 +8707,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8727,12 +8727,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>162145</t>
+          <t>158828</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>208778</t>
+          <t>209701</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>429912</t>
+          <t>435197</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>513227</t>
+          <t>516690</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>21,02%</t>
         </is>
       </c>
     </row>
@@ -8805,12 +8805,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>345810</t>
+          <t>346519</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>410788</t>
+          <t>415395</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>265397</t>
+          <t>263144</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>322935</t>
+          <t>323327</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>624476</t>
+          <t>627082</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>718286</t>
+          <t>718426</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8890,7 +8890,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -8918,12 +8918,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>605890</t>
+          <t>607478</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>683259</t>
+          <t>686802</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8953,12 +8953,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>425754</t>
+          <t>423906</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>488089</t>
+          <t>490949</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1054175</t>
+          <t>1049296</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1158521</t>
+          <t>1150451</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>46,79%</t>
         </is>
       </c>
     </row>
